--- a/analyses/brainage_gap/outputs/bootstrap/two_sample_bootstrap_summary.xlsx
+++ b/analyses/brainage_gap/outputs/bootstrap/two_sample_bootstrap_summary.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N19"/>
+  <dimension ref="A1:P45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,55 +446,65 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Bracket</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>N_Test</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>N_Ref</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Test_Mean_BAG</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Ref_Mean_BAG</t>
-        </is>
-      </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>Test_Mean</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Ref_Mean</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>Observed_Delta</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Bootstrap_Mean_Delta</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>CI_95_Lower</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>CI_95_Upper</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Contains_Zero</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>p_value</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Plot_Path</t>
         </is>
@@ -503,7 +513,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Chinese</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -516,46 +526,56 @@
           <t>40-90</t>
         </is>
       </c>
-      <c r="D2" t="n">
-        <v>326</v>
-      </c>
-      <c r="E2" t="n">
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>BAG</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>40a</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>159</v>
+      </c>
+      <c r="G2" t="n">
         <v>9493</v>
       </c>
-      <c r="F2" t="n">
-        <v>2.407634203579553</v>
-      </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
+        <v>1.363774017757769</v>
+      </c>
+      <c r="I2" t="n">
         <v>0.01420426200463499</v>
       </c>
-      <c r="H2" t="n">
-        <v>2.393429941574918</v>
-      </c>
-      <c r="I2" t="n">
-        <v>2.393512981626079</v>
-      </c>
       <c r="J2" t="n">
-        <v>1.920944595279782</v>
+        <v>1.349569755753134</v>
       </c>
       <c r="K2" t="n">
-        <v>2.873456762430285</v>
-      </c>
-      <c r="L2" t="b">
-        <v>0</v>
+        <v>1.349605065031553</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.7661961254299006</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>/Users/andrewli/Documents/Frangou Lab/BrainAGE/CentileBrain_BrainAGE/analyses/brainage_gap/outputs/bootstrap/Plots/Chinese/Chinese_Female_40-90_bootstrap_histogram.png</t>
+        <v>1.942919871634735</v>
+      </c>
+      <c r="N2" t="b">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>/Users/andrewli/Documents/Frangou Lab/BrainAGE/CentileBrain_BrainAGE/analyses/brainage_gap/outputs/bootstrap/Plots/Black/Black_Female_40-90_BAG_bootstrap_histogram.png</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Chinese</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -565,49 +585,59 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>5-40</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>547</v>
-      </c>
-      <c r="E3" t="n">
-        <v>8505</v>
+          <t>40-90</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>MAE</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>40a</t>
+        </is>
       </c>
       <c r="F3" t="n">
-        <v>2.167043180506354</v>
+        <v>159</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.008381465306172826</v>
+        <v>9493</v>
       </c>
       <c r="H3" t="n">
-        <v>2.175424645812527</v>
+        <v>3.20139752215051</v>
       </c>
       <c r="I3" t="n">
-        <v>2.176463676632026</v>
+        <v>3.083662273838618</v>
       </c>
       <c r="J3" t="n">
-        <v>1.914094743533056</v>
+        <v>0.1177352483118925</v>
       </c>
       <c r="K3" t="n">
-        <v>2.436171663079921</v>
-      </c>
-      <c r="L3" t="b">
-        <v>0</v>
+        <v>0.1173072434319</v>
+      </c>
+      <c r="L3" t="n">
+        <v>-0.2466784229135934</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>/Users/andrewli/Documents/Frangou Lab/BrainAGE/CentileBrain_BrainAGE/analyses/brainage_gap/outputs/bootstrap/Plots/Chinese/Chinese_Female_5-40_bootstrap_histogram.png</t>
+        <v>0.4896996649446345</v>
+      </c>
+      <c r="N3" t="b">
+        <v>1</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.5358000000000001</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>/Users/andrewli/Documents/Frangou Lab/BrainAGE/CentileBrain_BrainAGE/analyses/brainage_gap/outputs/bootstrap/Plots/Black/Black_Female_40-90_MAE_bootstrap_histogram.png</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Chinese</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -620,46 +650,56 @@
           <t>40-90</t>
         </is>
       </c>
-      <c r="D4" t="n">
-        <v>198</v>
-      </c>
-      <c r="E4" t="n">
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>BAG</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>40a</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>125</v>
+      </c>
+      <c r="G4" t="n">
         <v>7788</v>
       </c>
-      <c r="F4" t="n">
-        <v>2.29934150021436</v>
-      </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
+        <v>2.44134560861103</v>
+      </c>
+      <c r="I4" t="n">
         <v>-0.008569098016178771</v>
       </c>
-      <c r="H4" t="n">
-        <v>2.307910598230539</v>
-      </c>
-      <c r="I4" t="n">
-        <v>2.307834075494747</v>
-      </c>
       <c r="J4" t="n">
-        <v>1.690596367580195</v>
+        <v>2.449914706627208</v>
       </c>
       <c r="K4" t="n">
-        <v>2.936704545908253</v>
-      </c>
-      <c r="L4" t="b">
-        <v>0</v>
+        <v>2.444431695500775</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1.726054608206039</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>/Users/andrewli/Documents/Frangou Lab/BrainAGE/CentileBrain_BrainAGE/analyses/brainage_gap/outputs/bootstrap/Plots/Chinese/Chinese_Male_40-90_bootstrap_histogram.png</t>
+        <v>3.14616987224778</v>
+      </c>
+      <c r="N4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>/Users/andrewli/Documents/Frangou Lab/BrainAGE/CentileBrain_BrainAGE/analyses/brainage_gap/outputs/bootstrap/Plots/Black/Black_Male_40-90_BAG_bootstrap_histogram.png</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Chinese</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -669,49 +709,59 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>5-40</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>418</v>
-      </c>
-      <c r="E5" t="n">
-        <v>7541</v>
+          <t>40-90</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>MAE</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>40a</t>
+        </is>
       </c>
       <c r="F5" t="n">
-        <v>0.4370334934273646</v>
+        <v>125</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.003283886222118988</v>
+        <v>7788</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4403173796494836</v>
+        <v>3.839051567340491</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4405209478293967</v>
+        <v>3.229780626449666</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1046826324503152</v>
+        <v>0.6092709408908257</v>
       </c>
       <c r="K5" t="n">
-        <v>0.7830372641356681</v>
-      </c>
-      <c r="L5" t="b">
-        <v>0</v>
+        <v>0.609415987238862</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.1112232804851375</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0128</v>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>/Users/andrewli/Documents/Frangou Lab/BrainAGE/CentileBrain_BrainAGE/analyses/brainage_gap/outputs/bootstrap/Plots/Chinese/Chinese_Male_5-40_bootstrap_histogram.png</t>
+        <v>1.113914592353837</v>
+      </c>
+      <c r="N5" t="b">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.0162</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>/Users/andrewli/Documents/Frangou Lab/BrainAGE/CentileBrain_BrainAGE/analyses/brainage_gap/outputs/bootstrap/Plots/Black/Black_Male_40-90_MAE_bootstrap_histogram.png</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Japanese</t>
+          <t>Chilean</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -721,49 +771,59 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>40-90</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>187</v>
-      </c>
-      <c r="E6" t="n">
-        <v>9493</v>
+          <t>5-40</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>BAG</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>40bi</t>
+        </is>
       </c>
       <c r="F6" t="n">
-        <v>3.377495193717641</v>
+        <v>27</v>
       </c>
       <c r="G6" t="n">
-        <v>0.01420426200463499</v>
+        <v>8505</v>
       </c>
       <c r="H6" t="n">
-        <v>3.363290931713006</v>
+        <v>3.44301259731997</v>
       </c>
       <c r="I6" t="n">
-        <v>3.367321063749251</v>
+        <v>-0.008381465306172826</v>
       </c>
       <c r="J6" t="n">
-        <v>2.730591151941941</v>
+        <v>3.451394062626143</v>
       </c>
       <c r="K6" t="n">
-        <v>3.994999028398425</v>
-      </c>
-      <c r="L6" t="b">
-        <v>0</v>
+        <v>3.45349782855324</v>
+      </c>
+      <c r="L6" t="n">
+        <v>2.392579805040271</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>/Users/andrewli/Documents/Frangou Lab/BrainAGE/CentileBrain_BrainAGE/analyses/brainage_gap/outputs/bootstrap/Plots/Japanese/Japanese_Female_40-90_bootstrap_histogram.png</t>
+        <v>4.585123985658205</v>
+      </c>
+      <c r="N6" t="b">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>/Users/andrewli/Documents/Frangou Lab/BrainAGE/CentileBrain_BrainAGE/analyses/brainage_gap/outputs/bootstrap/Plots/Chilean/Chilean_Female_5-40_BAG_bootstrap_histogram.png</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Japanese</t>
+          <t>Chilean</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -776,46 +836,56 @@
           <t>5-40</t>
         </is>
       </c>
-      <c r="D7" t="n">
-        <v>216</v>
-      </c>
-      <c r="E7" t="n">
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>MAE</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>40bi</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>27</v>
+      </c>
+      <c r="G7" t="n">
         <v>8505</v>
       </c>
-      <c r="F7" t="n">
-        <v>-1.177027639772382</v>
-      </c>
-      <c r="G7" t="n">
-        <v>-0.008381465306172826</v>
-      </c>
       <c r="H7" t="n">
-        <v>-1.16864617446621</v>
+        <v>3.527012956891982</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.167455307069034</v>
+        <v>1.448046302578601</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.577270895911072</v>
+        <v>2.078966654313381</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.7609666619069009</v>
-      </c>
-      <c r="L7" t="b">
-        <v>0</v>
+        <v>2.0898955535242</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.105158079027466</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>/Users/andrewli/Documents/Frangou Lab/BrainAGE/CentileBrain_BrainAGE/analyses/brainage_gap/outputs/bootstrap/Plots/Japanese/Japanese_Female_5-40_bootstrap_histogram.png</t>
+        <v>3.185222863494975</v>
+      </c>
+      <c r="N7" t="b">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.0004</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>/Users/andrewli/Documents/Frangou Lab/BrainAGE/CentileBrain_BrainAGE/analyses/brainage_gap/outputs/bootstrap/Plots/Chilean/Chilean_Female_5-40_MAE_bootstrap_histogram.png</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Japanese</t>
+          <t>Chilean</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -825,49 +895,59 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>40-90</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>128</v>
-      </c>
-      <c r="E8" t="n">
-        <v>7788</v>
+          <t>5-40</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>BAG</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>40bi</t>
+        </is>
       </c>
       <c r="F8" t="n">
-        <v>3.239228039342565</v>
+        <v>56</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.008569098016178771</v>
+        <v>7541</v>
       </c>
       <c r="H8" t="n">
-        <v>3.247797137358743</v>
+        <v>2.08361888900311</v>
       </c>
       <c r="I8" t="n">
-        <v>3.251727217056401</v>
+        <v>-0.003283886222118988</v>
       </c>
       <c r="J8" t="n">
-        <v>2.482426989936308</v>
+        <v>2.086902775225229</v>
       </c>
       <c r="K8" t="n">
-        <v>4.024659440606289</v>
-      </c>
-      <c r="L8" t="b">
-        <v>0</v>
+        <v>2.086254351514392</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.164270275283332</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>/Users/andrewli/Documents/Frangou Lab/BrainAGE/CentileBrain_BrainAGE/analyses/brainage_gap/outputs/bootstrap/Plots/Japanese/Japanese_Male_40-90_bootstrap_histogram.png</t>
+        <v>3.007920145671059</v>
+      </c>
+      <c r="N8" t="b">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>/Users/andrewli/Documents/Frangou Lab/BrainAGE/CentileBrain_BrainAGE/analyses/brainage_gap/outputs/bootstrap/Plots/Chilean/Chilean_Male_5-40_BAG_bootstrap_histogram.png</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Japanese</t>
+          <t>Chilean</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -880,46 +960,56 @@
           <t>5-40</t>
         </is>
       </c>
-      <c r="D9" t="n">
-        <v>389</v>
-      </c>
-      <c r="E9" t="n">
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>MAE</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>40bi</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>56</v>
+      </c>
+      <c r="G9" t="n">
         <v>7541</v>
       </c>
-      <c r="F9" t="n">
-        <v>-0.7710055069016482</v>
-      </c>
-      <c r="G9" t="n">
-        <v>-0.003283886222118988</v>
-      </c>
       <c r="H9" t="n">
-        <v>-0.7677216206795292</v>
+        <v>3.395465014111248</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.7680547823656728</v>
+        <v>1.496159184830526</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.111854831324857</v>
+        <v>1.899305829280722</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.42486898609233</v>
-      </c>
-      <c r="L9" t="b">
-        <v>0</v>
+        <v>1.896970025473571</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.309697437765819</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>/Users/andrewli/Documents/Frangou Lab/BrainAGE/CentileBrain_BrainAGE/analyses/brainage_gap/outputs/bootstrap/Plots/Japanese/Japanese_Male_5-40_bootstrap_histogram.png</t>
+        <v>2.519557699482269</v>
+      </c>
+      <c r="N9" t="b">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>/Users/andrewli/Documents/Frangou Lab/BrainAGE/CentileBrain_BrainAGE/analyses/brainage_gap/outputs/bootstrap/Plots/Chilean/Chilean_Male_5-40_MAE_bootstrap_histogram.png</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Mexican</t>
+          <t>Chinese</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -932,46 +1022,56 @@
           <t>40-90</t>
         </is>
       </c>
-      <c r="D10" t="n">
-        <v>31</v>
-      </c>
-      <c r="E10" t="n">
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>BAG</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>40a</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>324</v>
+      </c>
+      <c r="G10" t="n">
         <v>9493</v>
       </c>
-      <c r="F10" t="n">
-        <v>6.252526153938822</v>
-      </c>
-      <c r="G10" t="n">
+      <c r="H10" t="n">
+        <v>2.432773870383416</v>
+      </c>
+      <c r="I10" t="n">
         <v>0.01420426200463499</v>
       </c>
-      <c r="H10" t="n">
-        <v>6.238321891934187</v>
-      </c>
-      <c r="I10" t="n">
-        <v>6.239856208034551</v>
-      </c>
       <c r="J10" t="n">
-        <v>4.845976156864998</v>
+        <v>2.41856960837878</v>
       </c>
       <c r="K10" t="n">
-        <v>7.608270433415865</v>
-      </c>
-      <c r="L10" t="b">
-        <v>0</v>
+        <v>2.419730366187397</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.936472538466184</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>/Users/andrewli/Documents/Frangou Lab/BrainAGE/CentileBrain_BrainAGE/analyses/brainage_gap/outputs/bootstrap/Plots/Mexican/Mexican_Female_40-90_bootstrap_histogram.png</t>
+        <v>2.906829792496624</v>
+      </c>
+      <c r="N10" t="b">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>/Users/andrewli/Documents/Frangou Lab/BrainAGE/CentileBrain_BrainAGE/analyses/brainage_gap/outputs/bootstrap/Plots/Chinese/Chinese_Female_40-90_BAG_bootstrap_histogram.png</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Mexican</t>
+          <t>Chinese</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -981,106 +1081,126 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>5-40</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>106</v>
-      </c>
-      <c r="E11" t="n">
-        <v>8505</v>
+          <t>40-90</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>MAE</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>40a</t>
+        </is>
       </c>
       <c r="F11" t="n">
-        <v>-0.9768102392205783</v>
+        <v>324</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.008381465306172826</v>
+        <v>9493</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.9684287739144055</v>
+        <v>3.891747656538398</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.9718828876980037</v>
+        <v>3.083662273838618</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.641505489360418</v>
+        <v>0.8080853826997805</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.3241073994601937</v>
-      </c>
-      <c r="L11" t="b">
-        <v>0</v>
+        <v>0.8067177548873354</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.4714753898110933</v>
       </c>
       <c r="M11" t="n">
-        <v>0.0018</v>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>/Users/andrewli/Documents/Frangou Lab/BrainAGE/CentileBrain_BrainAGE/analyses/brainage_gap/outputs/bootstrap/Plots/Mexican/Mexican_Female_5-40_bootstrap_histogram.png</t>
+        <v>1.14927473822725</v>
+      </c>
+      <c r="N11" t="b">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>/Users/andrewli/Documents/Frangou Lab/BrainAGE/CentileBrain_BrainAGE/analyses/brainage_gap/outputs/bootstrap/Plots/Chinese/Chinese_Female_40-90_MAE_bootstrap_histogram.png</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Mexican</t>
+          <t>Chinese</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>40-90</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>13</v>
-      </c>
-      <c r="E12" t="n">
-        <v>7788</v>
+          <t>5-40</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>BAG</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>40bi</t>
+        </is>
       </c>
       <c r="F12" t="n">
-        <v>-0.903863382798942</v>
+        <v>547</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.008569098016178771</v>
+        <v>8505</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.8952942847827632</v>
+        <v>2.167043180506354</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.8849709614522502</v>
+        <v>-0.008381465306172826</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.891500772318538</v>
+        <v>2.175424645812527</v>
       </c>
       <c r="K12" t="n">
-        <v>1.494647884946599</v>
-      </c>
-      <c r="L12" t="b">
-        <v>1</v>
+        <v>2.177233822327513</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1.920287884285917</v>
       </c>
       <c r="M12" t="n">
-        <v>0.4194</v>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>/Users/andrewli/Documents/Frangou Lab/BrainAGE/CentileBrain_BrainAGE/analyses/brainage_gap/outputs/bootstrap/Plots/Mexican/Mexican_Male_40-90_bootstrap_histogram.png</t>
+        <v>2.433872952634698</v>
+      </c>
+      <c r="N12" t="b">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>/Users/andrewli/Documents/Frangou Lab/BrainAGE/CentileBrain_BrainAGE/analyses/brainage_gap/outputs/bootstrap/Plots/Chinese/Chinese_Female_5-40_BAG_bootstrap_histogram.png</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Mexican</t>
+          <t>Chinese</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1088,51 +1208,61 @@
           <t>5-40</t>
         </is>
       </c>
-      <c r="D13" t="n">
-        <v>164</v>
-      </c>
-      <c r="E13" t="n">
-        <v>7541</v>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>MAE</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>40bi</t>
+        </is>
       </c>
       <c r="F13" t="n">
-        <v>-1.635154231932927</v>
+        <v>547</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.003283886222118988</v>
+        <v>8505</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.631870345710808</v>
+        <v>2.988168294188121</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.637222864864083</v>
+        <v>1.448046302578601</v>
       </c>
       <c r="J13" t="n">
-        <v>-2.210453861051695</v>
+        <v>1.54012199160952</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.060680024027247</v>
-      </c>
-      <c r="L13" t="b">
-        <v>0</v>
+        <v>1.540069716622705</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1.354731758144176</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>/Users/andrewli/Documents/Frangou Lab/BrainAGE/CentileBrain_BrainAGE/analyses/brainage_gap/outputs/bootstrap/Plots/Mexican/Mexican_Male_5-40_bootstrap_histogram.png</t>
+        <v>1.72976472839017</v>
+      </c>
+      <c r="N13" t="b">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>/Users/andrewli/Documents/Frangou Lab/BrainAGE/CentileBrain_BrainAGE/analyses/brainage_gap/outputs/bootstrap/Plots/Chinese/Chinese_Female_5-40_MAE_bootstrap_histogram.png</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Chinese</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1140,98 +1270,118 @@
           <t>40-90</t>
         </is>
       </c>
-      <c r="D14" t="n">
-        <v>144</v>
-      </c>
-      <c r="E14" t="n">
-        <v>9493</v>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>BAG</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>40a</t>
+        </is>
       </c>
       <c r="F14" t="n">
-        <v>2.000631904789214</v>
+        <v>194</v>
       </c>
       <c r="G14" t="n">
-        <v>0.01420426200463499</v>
+        <v>7788</v>
       </c>
       <c r="H14" t="n">
-        <v>1.98642764278458</v>
+        <v>2.200908610823356</v>
       </c>
       <c r="I14" t="n">
-        <v>1.987175952317989</v>
+        <v>-0.008569098016178771</v>
       </c>
       <c r="J14" t="n">
-        <v>1.31365257070585</v>
+        <v>2.209477708839535</v>
       </c>
       <c r="K14" t="n">
-        <v>2.661178656176318</v>
-      </c>
-      <c r="L14" t="b">
-        <v>0</v>
+        <v>2.206576554603842</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1.587115387135247</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>/Users/andrewli/Documents/Frangou Lab/BrainAGE/CentileBrain_BrainAGE/analyses/brainage_gap/outputs/bootstrap/Plots/South Asian/South Asian_Female_40-90_bootstrap_histogram.png</t>
+        <v>2.82199152907275</v>
+      </c>
+      <c r="N14" t="b">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>/Users/andrewli/Documents/Frangou Lab/BrainAGE/CentileBrain_BrainAGE/analyses/brainage_gap/outputs/bootstrap/Plots/Chinese/Chinese_Male_40-90_BAG_bootstrap_histogram.png</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Chinese</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>5-40</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>16</v>
-      </c>
-      <c r="E15" t="n">
-        <v>8505</v>
+          <t>40-90</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>MAE</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>40a</t>
+        </is>
       </c>
       <c r="F15" t="n">
-        <v>-0.3181752091999246</v>
+        <v>194</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.008381465306172826</v>
+        <v>7788</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.3097937438937518</v>
+        <v>3.786728959590673</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.312691172254368</v>
+        <v>3.229780626449666</v>
       </c>
       <c r="J15" t="n">
-        <v>-1.669611959807022</v>
+        <v>0.5569483331410074</v>
       </c>
       <c r="K15" t="n">
-        <v>1.139283596549988</v>
-      </c>
-      <c r="L15" t="b">
-        <v>1</v>
+        <v>0.5586355091054648</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.1420313067760833</v>
       </c>
       <c r="M15" t="n">
-        <v>0.6544</v>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>/Users/andrewli/Documents/Frangou Lab/BrainAGE/CentileBrain_BrainAGE/analyses/brainage_gap/outputs/bootstrap/Plots/South Asian/South Asian_Female_5-40_bootstrap_histogram.png</t>
+        <v>1.005280121648752</v>
+      </c>
+      <c r="N15" t="b">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>/Users/andrewli/Documents/Frangou Lab/BrainAGE/CentileBrain_BrainAGE/analyses/brainage_gap/outputs/bootstrap/Plots/Chinese/Chinese_Male_40-90_MAE_bootstrap_histogram.png</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Chinese</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1241,49 +1391,59 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>40-90</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>238</v>
-      </c>
-      <c r="E16" t="n">
-        <v>7788</v>
+          <t>5-40</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>BAG</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>40bi</t>
+        </is>
       </c>
       <c r="F16" t="n">
-        <v>2.464836462532876</v>
+        <v>418</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.008569098016178771</v>
+        <v>7541</v>
       </c>
       <c r="H16" t="n">
-        <v>2.473405560549054</v>
+        <v>0.4370334934273646</v>
       </c>
       <c r="I16" t="n">
-        <v>2.478258293812801</v>
+        <v>-0.003283886222118988</v>
       </c>
       <c r="J16" t="n">
-        <v>1.933472944158648</v>
+        <v>0.4403173796494836</v>
       </c>
       <c r="K16" t="n">
-        <v>3.019681818951145</v>
-      </c>
-      <c r="L16" t="b">
-        <v>0</v>
+        <v>0.435706235322352</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.09234867947784065</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>/Users/andrewli/Documents/Frangou Lab/BrainAGE/CentileBrain_BrainAGE/analyses/brainage_gap/outputs/bootstrap/Plots/South Asian/South Asian_Male_40-90_bootstrap_histogram.png</t>
+        <v>0.7852986434721486</v>
+      </c>
+      <c r="N16" t="b">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.0128</v>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>/Users/andrewli/Documents/Frangou Lab/BrainAGE/CentileBrain_BrainAGE/analyses/brainage_gap/outputs/bootstrap/Plots/Chinese/Chinese_Male_5-40_BAG_bootstrap_histogram.png</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Chinese</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1296,46 +1456,56 @@
           <t>5-40</t>
         </is>
       </c>
-      <c r="D17" t="n">
-        <v>21</v>
-      </c>
-      <c r="E17" t="n">
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>MAE</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>40bi</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>418</v>
+      </c>
+      <c r="G17" t="n">
         <v>7541</v>
       </c>
-      <c r="F17" t="n">
-        <v>0.06202825830603671</v>
-      </c>
-      <c r="G17" t="n">
-        <v>-0.003283886222118988</v>
-      </c>
       <c r="H17" t="n">
-        <v>0.0653121445281557</v>
+        <v>2.81899004980348</v>
       </c>
       <c r="I17" t="n">
-        <v>0.05999979171594005</v>
+        <v>1.496159184830526</v>
       </c>
       <c r="J17" t="n">
-        <v>-1.553284043567541</v>
+        <v>1.322830864972953</v>
       </c>
       <c r="K17" t="n">
-        <v>1.568108372517548</v>
-      </c>
-      <c r="L17" t="b">
-        <v>1</v>
+        <v>1.32346178542052</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1.11313575470976</v>
       </c>
       <c r="M17" t="n">
-        <v>0.9224</v>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>/Users/andrewli/Documents/Frangou Lab/BrainAGE/CentileBrain_BrainAGE/analyses/brainage_gap/outputs/bootstrap/Plots/South Asian/South Asian_Male_5-40_bootstrap_histogram.png</t>
+        <v>1.543263407273439</v>
+      </c>
+      <c r="N17" t="b">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>/Users/andrewli/Documents/Frangou Lab/BrainAGE/CentileBrain_BrainAGE/analyses/brainage_gap/outputs/bootstrap/Plots/Chinese/Chinese_Male_5-40_MAE_bootstrap_histogram.png</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Turkish</t>
+          <t>Japanese</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1345,94 +1515,1726 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>5-40</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>268</v>
-      </c>
-      <c r="E18" t="n">
-        <v>8505</v>
+          <t>40-90</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>BAG</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>40a</t>
+        </is>
       </c>
       <c r="F18" t="n">
-        <v>-0.4677516761140262</v>
+        <v>187</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.008381465306172826</v>
+        <v>9493</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.4593702108078534</v>
+        <v>3.377495193717641</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.4574885320587678</v>
+        <v>0.01420426200463499</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.8300815070584017</v>
+        <v>3.363290931713006</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.09550165968119266</v>
-      </c>
-      <c r="L18" t="b">
-        <v>0</v>
+        <v>3.358509077166233</v>
+      </c>
+      <c r="L18" t="n">
+        <v>2.737080681805085</v>
       </c>
       <c r="M18" t="n">
-        <v>0.0132</v>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>/Users/andrewli/Documents/Frangou Lab/BrainAGE/CentileBrain_BrainAGE/analyses/brainage_gap/outputs/bootstrap/Plots/Turkish/Turkish_Female_5-40_bootstrap_histogram.png</t>
+        <v>3.989214422935459</v>
+      </c>
+      <c r="N18" t="b">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>/Users/andrewli/Documents/Frangou Lab/BrainAGE/CentileBrain_BrainAGE/analyses/brainage_gap/outputs/bootstrap/Plots/Japanese/Japanese_Female_40-90_BAG_bootstrap_histogram.png</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>Japanese</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>40-90</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>MAE</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>40a</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>187</v>
+      </c>
+      <c r="G19" t="n">
+        <v>9493</v>
+      </c>
+      <c r="H19" t="n">
+        <v>4.562076869862906</v>
+      </c>
+      <c r="I19" t="n">
+        <v>3.083662273838618</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1.478414596024288</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1.477752397380567</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1.036226058233495</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1.933119460907988</v>
+      </c>
+      <c r="N19" t="b">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>/Users/andrewli/Documents/Frangou Lab/BrainAGE/CentileBrain_BrainAGE/analyses/brainage_gap/outputs/bootstrap/Plots/Japanese/Japanese_Female_40-90_MAE_bootstrap_histogram.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Japanese</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>5-40</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>BAG</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>40bi</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>216</v>
+      </c>
+      <c r="G20" t="n">
+        <v>8505</v>
+      </c>
+      <c r="H20" t="n">
+        <v>-1.177027639772382</v>
+      </c>
+      <c r="I20" t="n">
+        <v>-0.008381465306172826</v>
+      </c>
+      <c r="J20" t="n">
+        <v>-1.16864617446621</v>
+      </c>
+      <c r="K20" t="n">
+        <v>-1.168664024833109</v>
+      </c>
+      <c r="L20" t="n">
+        <v>-1.575043255098308</v>
+      </c>
+      <c r="M20" t="n">
+        <v>-0.7562095061258663</v>
+      </c>
+      <c r="N20" t="b">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>/Users/andrewli/Documents/Frangou Lab/BrainAGE/CentileBrain_BrainAGE/analyses/brainage_gap/outputs/bootstrap/Plots/Japanese/Japanese_Female_5-40_BAG_bootstrap_histogram.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Japanese</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>5-40</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>MAE</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>40bi</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>216</v>
+      </c>
+      <c r="G21" t="n">
+        <v>8505</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2.550990304857664</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1.448046302578601</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1.102944002279063</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1.101804871481319</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.8423922089903794</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1.37858727384429</v>
+      </c>
+      <c r="N21" t="b">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>/Users/andrewli/Documents/Frangou Lab/BrainAGE/CentileBrain_BrainAGE/analyses/brainage_gap/outputs/bootstrap/Plots/Japanese/Japanese_Female_5-40_MAE_bootstrap_histogram.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Japanese</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>40-90</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>BAG</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>40a</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>128</v>
+      </c>
+      <c r="G22" t="n">
+        <v>7788</v>
+      </c>
+      <c r="H22" t="n">
+        <v>3.239228039342565</v>
+      </c>
+      <c r="I22" t="n">
+        <v>-0.008569098016178771</v>
+      </c>
+      <c r="J22" t="n">
+        <v>3.247797137358743</v>
+      </c>
+      <c r="K22" t="n">
+        <v>3.252996891574568</v>
+      </c>
+      <c r="L22" t="n">
+        <v>2.485047760348707</v>
+      </c>
+      <c r="M22" t="n">
+        <v>4.036130646065244</v>
+      </c>
+      <c r="N22" t="b">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>/Users/andrewli/Documents/Frangou Lab/BrainAGE/CentileBrain_BrainAGE/analyses/brainage_gap/outputs/bootstrap/Plots/Japanese/Japanese_Male_40-90_BAG_bootstrap_histogram.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Japanese</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>40-90</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>MAE</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>40a</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>128</v>
+      </c>
+      <c r="G23" t="n">
+        <v>7788</v>
+      </c>
+      <c r="H23" t="n">
+        <v>4.367684813770984</v>
+      </c>
+      <c r="I23" t="n">
+        <v>3.229780626449666</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1.137904187321318</v>
+      </c>
+      <c r="K23" t="n">
+        <v>1.141567059239979</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0.5807364994153146</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1.728591292625812</v>
+      </c>
+      <c r="N23" t="b">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>/Users/andrewli/Documents/Frangou Lab/BrainAGE/CentileBrain_BrainAGE/analyses/brainage_gap/outputs/bootstrap/Plots/Japanese/Japanese_Male_40-90_MAE_bootstrap_histogram.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Japanese</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>5-40</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>BAG</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>40bi</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>389</v>
+      </c>
+      <c r="G24" t="n">
+        <v>7541</v>
+      </c>
+      <c r="H24" t="n">
+        <v>-0.7710055069016482</v>
+      </c>
+      <c r="I24" t="n">
+        <v>-0.003283886222118988</v>
+      </c>
+      <c r="J24" t="n">
+        <v>-0.7677216206795292</v>
+      </c>
+      <c r="K24" t="n">
+        <v>-0.7673994592642533</v>
+      </c>
+      <c r="L24" t="n">
+        <v>-1.108879502691958</v>
+      </c>
+      <c r="M24" t="n">
+        <v>-0.4288212708313266</v>
+      </c>
+      <c r="N24" t="b">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>/Users/andrewli/Documents/Frangou Lab/BrainAGE/CentileBrain_BrainAGE/analyses/brainage_gap/outputs/bootstrap/Plots/Japanese/Japanese_Male_5-40_BAG_bootstrap_histogram.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Japanese</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>5-40</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>MAE</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>40bi</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>389</v>
+      </c>
+      <c r="G25" t="n">
+        <v>7541</v>
+      </c>
+      <c r="H25" t="n">
+        <v>2.814730357072431</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1.496159184830526</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1.318571172241904</v>
+      </c>
+      <c r="K25" t="n">
+        <v>1.316584062507271</v>
+      </c>
+      <c r="L25" t="n">
+        <v>1.108499167077338</v>
+      </c>
+      <c r="M25" t="n">
+        <v>1.52730885704046</v>
+      </c>
+      <c r="N25" t="b">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>/Users/andrewli/Documents/Frangou Lab/BrainAGE/CentileBrain_BrainAGE/analyses/brainage_gap/outputs/bootstrap/Plots/Japanese/Japanese_Male_5-40_MAE_bootstrap_histogram.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Mexican</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>40-90</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>BAG</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>40a</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>31</v>
+      </c>
+      <c r="G26" t="n">
+        <v>9493</v>
+      </c>
+      <c r="H26" t="n">
+        <v>6.252526153938822</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.01420426200463499</v>
+      </c>
+      <c r="J26" t="n">
+        <v>6.238321891934187</v>
+      </c>
+      <c r="K26" t="n">
+        <v>6.237773240056862</v>
+      </c>
+      <c r="L26" t="n">
+        <v>4.829389381590799</v>
+      </c>
+      <c r="M26" t="n">
+        <v>7.621281685837251</v>
+      </c>
+      <c r="N26" t="b">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>/Users/andrewli/Documents/Frangou Lab/BrainAGE/CentileBrain_BrainAGE/analyses/brainage_gap/outputs/bootstrap/Plots/Mexican/Mexican_Female_40-90_BAG_bootstrap_histogram.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Mexican</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>40-90</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>MAE</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>40a</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>31</v>
+      </c>
+      <c r="G27" t="n">
+        <v>9493</v>
+      </c>
+      <c r="H27" t="n">
+        <v>6.497673760343709</v>
+      </c>
+      <c r="I27" t="n">
+        <v>3.083662273838618</v>
+      </c>
+      <c r="J27" t="n">
+        <v>3.414011486505091</v>
+      </c>
+      <c r="K27" t="n">
+        <v>3.416658019972377</v>
+      </c>
+      <c r="L27" t="n">
+        <v>2.218888733171737</v>
+      </c>
+      <c r="M27" t="n">
+        <v>4.669552822868007</v>
+      </c>
+      <c r="N27" t="b">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>/Users/andrewli/Documents/Frangou Lab/BrainAGE/CentileBrain_BrainAGE/analyses/brainage_gap/outputs/bootstrap/Plots/Mexican/Mexican_Female_40-90_MAE_bootstrap_histogram.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Mexican</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>5-40</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>BAG</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>40bi</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>106</v>
+      </c>
+      <c r="G28" t="n">
+        <v>8505</v>
+      </c>
+      <c r="H28" t="n">
+        <v>-0.9768102392205783</v>
+      </c>
+      <c r="I28" t="n">
+        <v>-0.008381465306172826</v>
+      </c>
+      <c r="J28" t="n">
+        <v>-0.9684287739144055</v>
+      </c>
+      <c r="K28" t="n">
+        <v>-0.9625468543506126</v>
+      </c>
+      <c r="L28" t="n">
+        <v>-1.637329410021698</v>
+      </c>
+      <c r="M28" t="n">
+        <v>-0.3044856828464997</v>
+      </c>
+      <c r="N28" t="b">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0.0036</v>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>/Users/andrewli/Documents/Frangou Lab/BrainAGE/CentileBrain_BrainAGE/analyses/brainage_gap/outputs/bootstrap/Plots/Mexican/Mexican_Female_5-40_BAG_bootstrap_histogram.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Mexican</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>5-40</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>MAE</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>40bi</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>106</v>
+      </c>
+      <c r="G29" t="n">
+        <v>8505</v>
+      </c>
+      <c r="H29" t="n">
+        <v>2.876220872815426</v>
+      </c>
+      <c r="I29" t="n">
+        <v>1.448046302578601</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1.428174570236825</v>
+      </c>
+      <c r="K29" t="n">
+        <v>1.42987384869599</v>
+      </c>
+      <c r="L29" t="n">
+        <v>1.02963172983536</v>
+      </c>
+      <c r="M29" t="n">
+        <v>1.865079136816632</v>
+      </c>
+      <c r="N29" t="b">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>/Users/andrewli/Documents/Frangou Lab/BrainAGE/CentileBrain_BrainAGE/analyses/brainage_gap/outputs/bootstrap/Plots/Mexican/Mexican_Female_5-40_MAE_bootstrap_histogram.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Mexican</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>40-90</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>BAG</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>40a</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>13</v>
+      </c>
+      <c r="G30" t="n">
+        <v>7788</v>
+      </c>
+      <c r="H30" t="n">
+        <v>-0.903863382798942</v>
+      </c>
+      <c r="I30" t="n">
+        <v>-0.008569098016178771</v>
+      </c>
+      <c r="J30" t="n">
+        <v>-0.8952942847827632</v>
+      </c>
+      <c r="K30" t="n">
+        <v>-0.9012304898640817</v>
+      </c>
+      <c r="L30" t="n">
+        <v>-2.917362377453423</v>
+      </c>
+      <c r="M30" t="n">
+        <v>1.471029419436226</v>
+      </c>
+      <c r="N30" t="b">
+        <v>1</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0.405</v>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>/Users/andrewli/Documents/Frangou Lab/BrainAGE/CentileBrain_BrainAGE/analyses/brainage_gap/outputs/bootstrap/Plots/Mexican/Mexican_Male_40-90_BAG_bootstrap_histogram.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Mexican</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>40-90</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>MAE</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>40a</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>13</v>
+      </c>
+      <c r="G31" t="n">
+        <v>7788</v>
+      </c>
+      <c r="H31" t="n">
+        <v>3.232578982110632</v>
+      </c>
+      <c r="I31" t="n">
+        <v>3.229780626449666</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0.002798355660965868</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0.01306703121174766</v>
+      </c>
+      <c r="L31" t="n">
+        <v>-1.235371198581728</v>
+      </c>
+      <c r="M31" t="n">
+        <v>1.545591397212462</v>
+      </c>
+      <c r="N31" t="b">
+        <v>1</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0.9644</v>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>/Users/andrewli/Documents/Frangou Lab/BrainAGE/CentileBrain_BrainAGE/analyses/brainage_gap/outputs/bootstrap/Plots/Mexican/Mexican_Male_40-90_MAE_bootstrap_histogram.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Mexican</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>5-40</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>BAG</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>40bi</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>164</v>
+      </c>
+      <c r="G32" t="n">
+        <v>7541</v>
+      </c>
+      <c r="H32" t="n">
+        <v>-1.635154231932927</v>
+      </c>
+      <c r="I32" t="n">
+        <v>-0.003283886222118988</v>
+      </c>
+      <c r="J32" t="n">
+        <v>-1.631870345710808</v>
+      </c>
+      <c r="K32" t="n">
+        <v>-1.634441937342445</v>
+      </c>
+      <c r="L32" t="n">
+        <v>-2.214292785597248</v>
+      </c>
+      <c r="M32" t="n">
+        <v>-1.069837984971053</v>
+      </c>
+      <c r="N32" t="b">
+        <v>0</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>/Users/andrewli/Documents/Frangou Lab/BrainAGE/CentileBrain_BrainAGE/analyses/brainage_gap/outputs/bootstrap/Plots/Mexican/Mexican_Male_5-40_BAG_bootstrap_histogram.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Mexican</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>5-40</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>MAE</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>40bi</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>164</v>
+      </c>
+      <c r="G33" t="n">
+        <v>7541</v>
+      </c>
+      <c r="H33" t="n">
+        <v>3.342757119408537</v>
+      </c>
+      <c r="I33" t="n">
+        <v>1.496159184830526</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1.84659793457801</v>
+      </c>
+      <c r="K33" t="n">
+        <v>1.844078029976633</v>
+      </c>
+      <c r="L33" t="n">
+        <v>1.482959549207941</v>
+      </c>
+      <c r="M33" t="n">
+        <v>2.20547255060331</v>
+      </c>
+      <c r="N33" t="b">
+        <v>0</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>/Users/andrewli/Documents/Frangou Lab/BrainAGE/CentileBrain_BrainAGE/analyses/brainage_gap/outputs/bootstrap/Plots/Mexican/Mexican_Male_5-40_MAE_bootstrap_histogram.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>40-90</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>BAG</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>40a</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>144</v>
+      </c>
+      <c r="G34" t="n">
+        <v>9493</v>
+      </c>
+      <c r="H34" t="n">
+        <v>2.000631904789214</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.01420426200463499</v>
+      </c>
+      <c r="J34" t="n">
+        <v>1.98642764278458</v>
+      </c>
+      <c r="K34" t="n">
+        <v>1.982577404180896</v>
+      </c>
+      <c r="L34" t="n">
+        <v>1.319982079712587</v>
+      </c>
+      <c r="M34" t="n">
+        <v>2.640076524508586</v>
+      </c>
+      <c r="N34" t="b">
+        <v>0</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>/Users/andrewli/Documents/Frangou Lab/BrainAGE/CentileBrain_BrainAGE/analyses/brainage_gap/outputs/bootstrap/Plots/South Asian/South Asian_Female_40-90_BAG_bootstrap_histogram.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>40-90</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>MAE</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>40a</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>144</v>
+      </c>
+      <c r="G35" t="n">
+        <v>9493</v>
+      </c>
+      <c r="H35" t="n">
+        <v>3.618056092100486</v>
+      </c>
+      <c r="I35" t="n">
+        <v>3.083662273838618</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0.5343938182618682</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0.5332158187383979</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0.08570897572304875</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0.9854932468507495</v>
+      </c>
+      <c r="N35" t="b">
+        <v>0</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0.0188</v>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>/Users/andrewli/Documents/Frangou Lab/BrainAGE/CentileBrain_BrainAGE/analyses/brainage_gap/outputs/bootstrap/Plots/South Asian/South Asian_Female_40-90_MAE_bootstrap_histogram.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>5-40</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>BAG</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>40bi</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>16</v>
+      </c>
+      <c r="G36" t="n">
+        <v>8505</v>
+      </c>
+      <c r="H36" t="n">
+        <v>-0.3181752091999246</v>
+      </c>
+      <c r="I36" t="n">
+        <v>-0.008381465306172826</v>
+      </c>
+      <c r="J36" t="n">
+        <v>-0.3097937438937518</v>
+      </c>
+      <c r="K36" t="n">
+        <v>-0.3155596400248057</v>
+      </c>
+      <c r="L36" t="n">
+        <v>-1.675941685864466</v>
+      </c>
+      <c r="M36" t="n">
+        <v>1.102871217434337</v>
+      </c>
+      <c r="N36" t="b">
+        <v>1</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0.6452</v>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>/Users/andrewli/Documents/Frangou Lab/BrainAGE/CentileBrain_BrainAGE/analyses/brainage_gap/outputs/bootstrap/Plots/South Asian/South Asian_Female_5-40_BAG_bootstrap_histogram.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>5-40</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>MAE</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>40bi</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>16</v>
+      </c>
+      <c r="G37" t="n">
+        <v>8505</v>
+      </c>
+      <c r="H37" t="n">
+        <v>2.177530382264464</v>
+      </c>
+      <c r="I37" t="n">
+        <v>1.448046302578601</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0.7294840796858637</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0.7296639686264793</v>
+      </c>
+      <c r="L37" t="n">
+        <v>-0.1461903514488073</v>
+      </c>
+      <c r="M37" t="n">
+        <v>1.71628742262663</v>
+      </c>
+      <c r="N37" t="b">
+        <v>1</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0.1144</v>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>/Users/andrewli/Documents/Frangou Lab/BrainAGE/CentileBrain_BrainAGE/analyses/brainage_gap/outputs/bootstrap/Plots/South Asian/South Asian_Female_5-40_MAE_bootstrap_histogram.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>40-90</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>BAG</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>40a</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>238</v>
+      </c>
+      <c r="G38" t="n">
+        <v>7788</v>
+      </c>
+      <c r="H38" t="n">
+        <v>2.464836462532876</v>
+      </c>
+      <c r="I38" t="n">
+        <v>-0.008569098016178771</v>
+      </c>
+      <c r="J38" t="n">
+        <v>2.473405560549054</v>
+      </c>
+      <c r="K38" t="n">
+        <v>2.469887470819128</v>
+      </c>
+      <c r="L38" t="n">
+        <v>1.935894030413875</v>
+      </c>
+      <c r="M38" t="n">
+        <v>3.011574162593468</v>
+      </c>
+      <c r="N38" t="b">
+        <v>0</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>/Users/andrewli/Documents/Frangou Lab/BrainAGE/CentileBrain_BrainAGE/analyses/brainage_gap/outputs/bootstrap/Plots/South Asian/South Asian_Male_40-90_BAG_bootstrap_histogram.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>40-90</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>MAE</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>40a</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>238</v>
+      </c>
+      <c r="G39" t="n">
+        <v>7788</v>
+      </c>
+      <c r="H39" t="n">
+        <v>3.924168775186589</v>
+      </c>
+      <c r="I39" t="n">
+        <v>3.229780626449666</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0.6943881487369232</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0.6909638502800186</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0.310239561727326</v>
+      </c>
+      <c r="M39" t="n">
+        <v>1.063044013756986</v>
+      </c>
+      <c r="N39" t="b">
+        <v>0</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>/Users/andrewli/Documents/Frangou Lab/BrainAGE/CentileBrain_BrainAGE/analyses/brainage_gap/outputs/bootstrap/Plots/South Asian/South Asian_Male_40-90_MAE_bootstrap_histogram.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>5-40</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>BAG</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>40bi</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>21</v>
+      </c>
+      <c r="G40" t="n">
+        <v>7541</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.06202825830603671</v>
+      </c>
+      <c r="I40" t="n">
+        <v>-0.003283886222118988</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0.0653121445281557</v>
+      </c>
+      <c r="K40" t="n">
+        <v>0.06886499286243598</v>
+      </c>
+      <c r="L40" t="n">
+        <v>-1.558333738121577</v>
+      </c>
+      <c r="M40" t="n">
+        <v>1.592151319628082</v>
+      </c>
+      <c r="N40" t="b">
+        <v>1</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0.9208</v>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>/Users/andrewli/Documents/Frangou Lab/BrainAGE/CentileBrain_BrainAGE/analyses/brainage_gap/outputs/bootstrap/Plots/South Asian/South Asian_Male_5-40_BAG_bootstrap_histogram.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>5-40</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>MAE</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>40bi</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>21</v>
+      </c>
+      <c r="G41" t="n">
+        <v>7541</v>
+      </c>
+      <c r="H41" t="n">
+        <v>2.707086686322044</v>
+      </c>
+      <c r="I41" t="n">
+        <v>1.496159184830526</v>
+      </c>
+      <c r="J41" t="n">
+        <v>1.210927501491518</v>
+      </c>
+      <c r="K41" t="n">
+        <v>1.204265144501429</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0.2363408812786714</v>
+      </c>
+      <c r="M41" t="n">
+        <v>2.317934385278381</v>
+      </c>
+      <c r="N41" t="b">
+        <v>0</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0.0116</v>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>/Users/andrewli/Documents/Frangou Lab/BrainAGE/CentileBrain_BrainAGE/analyses/brainage_gap/outputs/bootstrap/Plots/South Asian/South Asian_Male_5-40_MAE_bootstrap_histogram.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
           <t>Turkish</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>5-40</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>BAG</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>40bi</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>268</v>
+      </c>
+      <c r="G42" t="n">
+        <v>8505</v>
+      </c>
+      <c r="H42" t="n">
+        <v>-0.4677516761140262</v>
+      </c>
+      <c r="I42" t="n">
+        <v>-0.008381465306172826</v>
+      </c>
+      <c r="J42" t="n">
+        <v>-0.4593702108078534</v>
+      </c>
+      <c r="K42" t="n">
+        <v>-0.4534907770200782</v>
+      </c>
+      <c r="L42" t="n">
+        <v>-0.8192491468985933</v>
+      </c>
+      <c r="M42" t="n">
+        <v>-0.0879646651594865</v>
+      </c>
+      <c r="N42" t="b">
+        <v>0</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0.0158</v>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>/Users/andrewli/Documents/Frangou Lab/BrainAGE/CentileBrain_BrainAGE/analyses/brainage_gap/outputs/bootstrap/Plots/Turkish/Turkish_Female_5-40_BAG_bootstrap_histogram.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Turkish</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>5-40</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>MAE</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>40bi</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>268</v>
+      </c>
+      <c r="G43" t="n">
+        <v>8505</v>
+      </c>
+      <c r="H43" t="n">
+        <v>2.414725820022386</v>
+      </c>
+      <c r="I43" t="n">
+        <v>1.448046302578601</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0.966679517443785</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0.9670201326539822</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0.7498352702621187</v>
+      </c>
+      <c r="M43" t="n">
+        <v>1.197490292223811</v>
+      </c>
+      <c r="N43" t="b">
+        <v>0</v>
+      </c>
+      <c r="O43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>/Users/andrewli/Documents/Frangou Lab/BrainAGE/CentileBrain_BrainAGE/analyses/brainage_gap/outputs/bootstrap/Plots/Turkish/Turkish_Female_5-40_MAE_bootstrap_histogram.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Turkish</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C44" t="inlineStr">
         <is>
           <t>5-40</t>
         </is>
       </c>
-      <c r="D19" t="n">
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>BAG</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>40bi</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
         <v>154</v>
       </c>
-      <c r="E19" t="n">
+      <c r="G44" t="n">
         <v>7541</v>
       </c>
-      <c r="F19" t="n">
+      <c r="H44" t="n">
         <v>-0.2471475670944699</v>
       </c>
-      <c r="G19" t="n">
+      <c r="I44" t="n">
         <v>-0.003283886222118988</v>
       </c>
-      <c r="H19" t="n">
+      <c r="J44" t="n">
         <v>-0.2438636808723509</v>
       </c>
-      <c r="I19" t="n">
-        <v>-0.2442610234558997</v>
-      </c>
-      <c r="J19" t="n">
-        <v>-0.7826373055310082</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0.2942474234637759</v>
-      </c>
-      <c r="L19" t="b">
+      <c r="K44" t="n">
+        <v>-0.2433044005910204</v>
+      </c>
+      <c r="L44" t="n">
+        <v>-0.7756787191848432</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0.2870909225226589</v>
+      </c>
+      <c r="N44" t="b">
         <v>1</v>
       </c>
-      <c r="M19" t="n">
-        <v>0.3768</v>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>/Users/andrewli/Documents/Frangou Lab/BrainAGE/CentileBrain_BrainAGE/analyses/brainage_gap/outputs/bootstrap/Plots/Turkish/Turkish_Male_5-40_bootstrap_histogram.png</t>
+      <c r="O44" t="n">
+        <v>0.3714</v>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>/Users/andrewli/Documents/Frangou Lab/BrainAGE/CentileBrain_BrainAGE/analyses/brainage_gap/outputs/bootstrap/Plots/Turkish/Turkish_Male_5-40_BAG_bootstrap_histogram.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Turkish</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>5-40</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>MAE</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>40bi</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>154</v>
+      </c>
+      <c r="G45" t="n">
+        <v>7541</v>
+      </c>
+      <c r="H45" t="n">
+        <v>2.709167943982263</v>
+      </c>
+      <c r="I45" t="n">
+        <v>1.496159184830526</v>
+      </c>
+      <c r="J45" t="n">
+        <v>1.213008759151737</v>
+      </c>
+      <c r="K45" t="n">
+        <v>1.212243065738668</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0.8948096606652448</v>
+      </c>
+      <c r="M45" t="n">
+        <v>1.540968975869512</v>
+      </c>
+      <c r="N45" t="b">
+        <v>0</v>
+      </c>
+      <c r="O45" t="n">
+        <v>0</v>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>/Users/andrewli/Documents/Frangou Lab/BrainAGE/CentileBrain_BrainAGE/analyses/brainage_gap/outputs/bootstrap/Plots/Turkish/Turkish_Male_5-40_MAE_bootstrap_histogram.png</t>
         </is>
       </c>
     </row>
